--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationrequest.xlsx
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -648,7 +648,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -742,7 +742,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -959,7 +959,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1200,7 +1200,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1469,7 +1469,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2066,7 +2066,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2089,7 +2089,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2108,7 +2108,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
